--- a/Analyst.xlsx
+++ b/Analyst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\MLBB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D05E6D-C069-4C0A-9457-8856772A22F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D0A4FE-9FCB-475F-835B-FD272A1C384E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{BF18B510-6A1A-4009-95A3-8CBEC6D17C32}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Hero Data'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MLBB Statistics'!$A$3:$AO$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MLBB Statistics'!$A$3:$AO$128</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3806" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3831" uniqueCount="205">
   <si>
     <t>Team</t>
   </si>
@@ -894,6 +894,33 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -915,35 +942,8 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1345,10 +1345,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B396CDEB-245E-4121-A936-7C995A7B760B}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:AO127"/>
+  <dimension ref="A1:AO128"/>
   <sheetFormatPr defaultColWidth="12.69921875" defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.69921875" style="10"/>
@@ -1364,97 +1364,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="15" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="O1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="28" t="s">
+      <c r="P1" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="15" t="s">
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="24" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="16" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17" t="s">
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+      <c r="H2" s="26"/>
+      <c r="I2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="19" t="s">
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="19"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="20" t="s">
+      <c r="M2" s="28"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="17" t="s">
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="17"/>
-      <c r="U2" s="23" t="s">
+      <c r="T2" s="26"/>
+      <c r="U2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="19" t="s">
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="Y2" s="19"/>
-      <c r="Z2" s="15"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="24"/>
     </row>
     <row r="3" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="22"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="23"/>
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1485,8 +1485,8 @@
       <c r="M3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="15"/>
-      <c r="O3" s="22"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="23"/>
       <c r="P3" s="11" t="s">
         <v>6</v>
       </c>
@@ -1517,9 +1517,9 @@
       <c r="Y3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Z3" s="15"/>
-    </row>
-    <row r="4" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z3" s="24"/>
+    </row>
+    <row r="4" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>105</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>105</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>105</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>105</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>105</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>105</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>105</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>105</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>105</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>105</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>105</v>
       </c>
@@ -2410,7 +2410,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>105</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>105</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>105</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>105</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>105</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>105</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>105</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>105</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>105</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>105</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>105</v>
       </c>
@@ -3301,7 +3301,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>105</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>105</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>105</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>105</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>105</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>105</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>105</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>105</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>105</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>105</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>105</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>105</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>105</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>105</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>105</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>105</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>105</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="43" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>105</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="44" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>105</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="45" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>105</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>105</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>105</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>105</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="49" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>105</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="50" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>105</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="51" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>105</v>
       </c>
@@ -5407,7 +5407,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="52" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>105</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="53" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>105</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="54" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>105</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="55" spans="1:41" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:41" s="6" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>105</v>
       </c>
@@ -5746,7 +5746,7 @@
       <c r="AN55" s="1"/>
       <c r="AO55" s="1"/>
     </row>
-    <row r="56" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
         <v>105</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="57" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>105</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="58" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>105</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="59" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>105</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="60" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>105</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="61" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
         <v>105</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="62" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>105</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="63" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>105</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="64" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>105</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="65" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>105</v>
       </c>
@@ -6556,7 +6556,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="66" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
         <v>105</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="67" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
         <v>105</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="68" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>105</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="69" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
         <v>105</v>
       </c>
@@ -6876,11 +6876,11 @@
         <v>30</v>
       </c>
       <c r="Z69" s="4" t="str">
-        <f t="shared" ref="Z69:Z127" si="1">IF(N69="WIN","LOSE","WIN")</f>
+        <f t="shared" ref="Z69:Z128" si="1">IF(N69="WIN","LOSE","WIN")</f>
         <v>WIN</v>
       </c>
     </row>
-    <row r="70" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
         <v>105</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="71" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
         <v>105</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="72" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
         <v>105</v>
       </c>
@@ -7123,7 +7123,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="73" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
         <v>105</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="74" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>105</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="75" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>105</v>
       </c>
@@ -7366,7 +7366,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="76" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>105</v>
       </c>
@@ -7447,7 +7447,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="77" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>105</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="78" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>105</v>
       </c>
@@ -7609,7 +7609,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="79" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>105</v>
       </c>
@@ -7690,7 +7690,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="80" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
         <v>105</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="81" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
         <v>105</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="82" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>105</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="83" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
         <v>105</v>
       </c>
@@ -8014,7 +8014,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="84" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>105</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="85" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
         <v>105</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="86" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
         <v>105</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="87" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
         <v>105</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="88" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>105</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="89" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
         <v>105</v>
       </c>
@@ -8500,7 +8500,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="90" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
         <v>105</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="91" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
         <v>105</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="92" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>105</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="93" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
         <v>105</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="94" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
         <v>105</v>
       </c>
@@ -8905,7 +8905,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="95" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
         <v>105</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="96" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
         <v>105</v>
       </c>
@@ -9067,7 +9067,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="97" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
         <v>105</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="98" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>105</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="99" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
         <v>105</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="100" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
         <v>105</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="101" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
         <v>105</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="102" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
         <v>105</v>
       </c>
@@ -9553,7 +9553,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="103" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
         <v>105</v>
       </c>
@@ -9634,7 +9634,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="104" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
         <v>105</v>
       </c>
@@ -9715,7 +9715,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="105" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
         <v>85</v>
       </c>
@@ -9796,7 +9796,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="106" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
         <v>85</v>
       </c>
@@ -9877,7 +9877,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="107" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
         <v>85</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="108" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
         <v>85</v>
       </c>
@@ -10054,7 +10054,7 @@
       <c r="AN108" s="6"/>
       <c r="AO108" s="6"/>
     </row>
-    <row r="109" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
         <v>85</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="110" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
         <v>85</v>
       </c>
@@ -10216,7 +10216,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="111" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
         <v>85</v>
       </c>
@@ -10297,7 +10297,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="112" spans="1:41" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:41" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
         <v>85</v>
       </c>
@@ -10378,7 +10378,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="113" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
         <v>85</v>
       </c>
@@ -10459,7 +10459,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="114" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
         <v>85</v>
       </c>
@@ -10540,7 +10540,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="115" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
         <v>85</v>
       </c>
@@ -10621,7 +10621,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="116" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
         <v>85</v>
       </c>
@@ -10702,7 +10702,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="117" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
         <v>85</v>
       </c>
@@ -10783,7 +10783,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="118" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
         <v>85</v>
       </c>
@@ -10864,7 +10864,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="119" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
         <v>85</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="120" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
         <v>85</v>
       </c>
@@ -11026,7 +11026,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="121" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
         <v>85</v>
       </c>
@@ -11350,7 +11350,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="125" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
         <v>85</v>
       </c>
@@ -11431,7 +11431,7 @@
         <v>LOSE</v>
       </c>
     </row>
-    <row r="126" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
         <v>85</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>WIN</v>
       </c>
     </row>
-    <row r="127" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
         <v>85</v>
       </c>
@@ -11593,8 +11593,94 @@
         <v>WIN</v>
       </c>
     </row>
+    <row r="128" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I128" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J128" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K128" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L128" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M128" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N128" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O128" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="P128" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q128" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R128" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S128" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="T128" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U128" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V128" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="W128" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X128" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y128" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z128" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>LOSE</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:AO3" xr:uid="{B396CDEB-245E-4121-A936-7C995A7B760B}">
+  <autoFilter ref="A3:AO128" xr:uid="{B396CDEB-245E-4121-A936-7C995A7B760B}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="TNC"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:AO127">
       <sortCondition ref="A3"/>
     </sortState>
@@ -11618,7 +11704,7 @@
     <mergeCell ref="X2:Y2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="N1:N1048576 Z4:Z127">
+  <conditionalFormatting sqref="N1:N1048576 Z4:Z128">
     <cfRule type="cellIs" dxfId="7" priority="11" operator="equal">
       <formula>"win"</formula>
     </cfRule>
@@ -11662,4262 +11748,4262 @@
   <dimension ref="A1:J133"/>
   <sheetFormatPr defaultColWidth="12.69921875" defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="12.69921875" style="29"/>
+    <col min="1" max="16384" width="12.69921875" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="16" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" s="29" t="s">
+      <c r="C2" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E2" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="31">
+      <c r="E2" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="17">
         <v>4</v>
       </c>
-      <c r="G2" s="31">
+      <c r="G2" s="17">
         <v>8</v>
       </c>
-      <c r="H2" s="31">
+      <c r="H2" s="17">
         <v>1</v>
       </c>
-      <c r="I2" s="31">
+      <c r="I2" s="17">
         <v>4</v>
       </c>
-      <c r="J2" s="31">
+      <c r="J2" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="29" t="s">
+      <c r="C3" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="31">
+      <c r="F3" s="17">
         <v>8</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="17">
         <v>4</v>
       </c>
-      <c r="H3" s="31">
+      <c r="H3" s="17">
         <v>9</v>
       </c>
-      <c r="I3" s="31">
+      <c r="I3" s="17">
         <v>3</v>
       </c>
-      <c r="J3" s="31">
+      <c r="J3" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="29" t="s">
+      <c r="C4" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="17">
         <v>7</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="17">
         <v>7</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="17">
         <v>1</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="17">
         <v>3</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="17">
         <v>8</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="17">
         <v>4</v>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="17">
         <v>5</v>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="17">
         <v>5</v>
       </c>
-      <c r="J5" s="31">
+      <c r="J5" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="29" t="s">
+      <c r="C6" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="17">
         <v>6</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="17">
         <v>7</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="17">
         <v>4</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="17">
         <v>3</v>
       </c>
-      <c r="J6" s="31">
+      <c r="J6" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F7" s="31">
+      <c r="E7" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" s="17">
         <v>6</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="17">
         <v>7</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="17">
         <v>1</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="17">
         <v>4</v>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="29" t="s">
+      <c r="C8" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8" s="31">
+      <c r="E8" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="17">
         <v>6</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="17">
         <v>3</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="17">
         <v>5</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="17">
         <v>2</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="29" t="s">
+      <c r="C9" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="17">
         <v>4</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="17">
         <v>8</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="17">
         <v>3</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="17">
         <v>4</v>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="17">
         <v>6</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="17">
         <v>6</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="17">
         <v>7</v>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="17">
         <v>5</v>
       </c>
-      <c r="J10" s="31">
+      <c r="J10" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C11" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="29" t="s">
+      <c r="C11" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F11" s="31">
+      <c r="E11" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" s="17">
         <v>7</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="17">
         <v>1</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="17">
         <v>9</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="17">
         <v>3</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="29" t="s">
+      <c r="C12" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F12" s="31">
+      <c r="E12" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="17">
         <v>5</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="17">
         <v>8</v>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="17">
         <v>1</v>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="17">
         <v>4</v>
       </c>
-      <c r="J12" s="31">
+      <c r="J12" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C13" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D13" s="29" t="s">
+      <c r="C13" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E13" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F13" s="31">
+      <c r="E13" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" s="17">
         <v>3</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="17">
         <v>7</v>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="17">
         <v>7</v>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="17">
         <v>1</v>
       </c>
-      <c r="J13" s="31">
+      <c r="J13" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C14" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="29" t="s">
+      <c r="C14" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="17">
         <v>7</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="17">
         <v>5</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="17">
         <v>7</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="17">
         <v>6</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" s="29" t="s">
+      <c r="C15" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="17">
         <v>7</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="17">
         <v>5</v>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="17">
         <v>1</v>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="17">
         <v>3</v>
       </c>
-      <c r="J15" s="31">
+      <c r="J15" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="17">
         <v>4</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="17">
         <v>8</v>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="17">
         <v>6</v>
       </c>
-      <c r="I16" s="31">
+      <c r="I16" s="17">
         <v>2</v>
       </c>
-      <c r="J16" s="31">
+      <c r="J16" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="17">
         <v>9</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="17">
         <v>3</v>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="17">
         <v>8</v>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="17">
         <v>2</v>
       </c>
-      <c r="J17" s="31">
+      <c r="J17" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" s="29" t="s">
+      <c r="C18" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="17">
         <v>10</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="17">
         <v>4</v>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="17">
         <v>6</v>
       </c>
-      <c r="I18" s="31">
+      <c r="I18" s="17">
         <v>5</v>
       </c>
-      <c r="J18" s="31">
+      <c r="J18" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C19" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" s="29" t="s">
+      <c r="C19" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F19" s="31">
+      <c r="E19" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" s="17">
         <v>3</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="17">
         <v>8</v>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="17">
         <v>1</v>
       </c>
-      <c r="I19" s="31">
+      <c r="I19" s="17">
         <v>2</v>
       </c>
-      <c r="J19" s="31">
+      <c r="J19" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="29" t="s">
+      <c r="C20" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="E20" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="17">
         <v>10</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="17">
         <v>3</v>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="17">
         <v>8</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="17">
         <v>2</v>
       </c>
-      <c r="J20" s="31">
+      <c r="J20" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="29" t="s">
+      <c r="E21" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="17">
         <v>5</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="17">
         <v>8</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="17">
         <v>3</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="17">
         <v>8</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="17">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22" s="29" t="s">
+      <c r="C22" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F22" s="31">
+      <c r="E22" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" s="17">
         <v>3</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="17">
         <v>8</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="17">
         <v>4</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="17">
         <v>2</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" s="29" t="s">
+      <c r="C23" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E23" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F23" s="31">
+      <c r="E23" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" s="17">
         <v>2</v>
       </c>
-      <c r="G23" s="31">
+      <c r="G23" s="17">
         <v>8</v>
       </c>
-      <c r="H23" s="31">
+      <c r="H23" s="17">
         <v>2</v>
       </c>
-      <c r="I23" s="31">
+      <c r="I23" s="17">
         <v>3</v>
       </c>
-      <c r="J23" s="31">
+      <c r="J23" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E24" s="29" t="s">
+      <c r="E24" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="17">
         <v>9</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="17">
         <v>2</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="17">
         <v>8</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="17">
         <v>3</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25" s="29" t="s">
+      <c r="C25" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E25" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F25" s="31">
+      <c r="E25" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" s="17">
         <v>4</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="17">
         <v>9</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="17">
         <v>6</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="17">
         <v>2</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C26" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" s="29" t="s">
+      <c r="C26" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E26" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F26" s="31">
+      <c r="E26" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" s="17">
         <v>3</v>
       </c>
-      <c r="G26" s="31">
+      <c r="G26" s="17">
         <v>8</v>
       </c>
-      <c r="H26" s="31">
+      <c r="H26" s="17">
         <v>2</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="17">
         <v>1</v>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E27" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F27" s="31">
+      <c r="E27" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" s="17">
         <v>7</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="17">
         <v>2</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="17">
         <v>6</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="17">
         <v>7</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C28" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28" s="29" t="s">
+      <c r="C28" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="17">
         <v>7</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="17">
         <v>5</v>
       </c>
-      <c r="H28" s="31">
+      <c r="H28" s="17">
         <v>7</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="17">
         <v>7</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C29" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" s="29" t="s">
+      <c r="C29" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E29" s="29" t="s">
+      <c r="E29" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="17">
         <v>7</v>
       </c>
-      <c r="G29" s="31">
+      <c r="G29" s="17">
         <v>6</v>
       </c>
-      <c r="H29" s="31">
+      <c r="H29" s="17">
         <v>4</v>
       </c>
-      <c r="I29" s="31">
+      <c r="I29" s="17">
         <v>4</v>
       </c>
-      <c r="J29" s="31">
+      <c r="J29" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C30" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E30" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F30" s="31">
+      <c r="E30" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" s="17">
         <v>4</v>
       </c>
-      <c r="G30" s="31">
+      <c r="G30" s="17">
         <v>9</v>
       </c>
-      <c r="H30" s="31">
+      <c r="H30" s="17">
         <v>1</v>
       </c>
-      <c r="I30" s="31">
+      <c r="I30" s="17">
         <v>7</v>
       </c>
-      <c r="J30" s="31">
+      <c r="J30" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C31" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D31" s="29" t="s">
+      <c r="C31" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E31" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F31" s="31">
+      <c r="E31" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" s="17">
         <v>3</v>
       </c>
-      <c r="G31" s="31">
+      <c r="G31" s="17">
         <v>8</v>
       </c>
-      <c r="H31" s="31">
+      <c r="H31" s="17">
         <v>3</v>
       </c>
-      <c r="I31" s="31">
+      <c r="I31" s="17">
         <v>2</v>
       </c>
-      <c r="J31" s="31">
+      <c r="J31" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C32" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" s="29" t="s">
+      <c r="C32" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E32" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F32" s="31">
+      <c r="E32" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="17">
         <v>3</v>
       </c>
-      <c r="G32" s="31">
+      <c r="G32" s="17">
         <v>8</v>
       </c>
-      <c r="H32" s="31">
+      <c r="H32" s="17">
         <v>5</v>
       </c>
-      <c r="I32" s="31">
+      <c r="I32" s="17">
         <v>2</v>
       </c>
-      <c r="J32" s="31">
+      <c r="J32" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C33" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D33" s="29" t="s">
+      <c r="C33" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E33" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33" s="31">
+      <c r="E33" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" s="17">
         <v>5</v>
       </c>
-      <c r="G33" s="31">
+      <c r="G33" s="17">
         <v>3</v>
       </c>
-      <c r="H33" s="31">
+      <c r="H33" s="17">
         <v>2</v>
       </c>
-      <c r="I33" s="31">
+      <c r="I33" s="17">
         <v>1</v>
       </c>
-      <c r="J33" s="31">
+      <c r="J33" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C34" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" s="29" t="s">
+      <c r="C34" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E34" s="29" t="s">
+      <c r="E34" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F34" s="31">
+      <c r="F34" s="17">
         <v>7</v>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="17">
         <v>7</v>
       </c>
-      <c r="H34" s="31">
+      <c r="H34" s="17">
         <v>1</v>
       </c>
-      <c r="I34" s="31">
+      <c r="I34" s="17">
         <v>4</v>
       </c>
-      <c r="J34" s="31">
+      <c r="J34" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="D35" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E35" s="29" t="s">
+      <c r="E35" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F35" s="31">
+      <c r="F35" s="17">
         <v>8</v>
       </c>
-      <c r="G35" s="31">
+      <c r="G35" s="17">
         <v>6</v>
       </c>
-      <c r="H35" s="31">
+      <c r="H35" s="17">
         <v>9</v>
       </c>
-      <c r="I35" s="31">
+      <c r="I35" s="17">
         <v>2</v>
       </c>
-      <c r="J35" s="31">
+      <c r="J35" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="29" t="s">
+      <c r="B36" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D36" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="29" t="s">
+      <c r="E36" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F36" s="31">
+      <c r="F36" s="17">
         <v>9</v>
       </c>
-      <c r="G36" s="31">
+      <c r="G36" s="17">
         <v>3</v>
       </c>
-      <c r="H36" s="31">
+      <c r="H36" s="17">
         <v>2</v>
       </c>
-      <c r="I36" s="31">
+      <c r="I36" s="17">
         <v>6</v>
       </c>
-      <c r="J36" s="31">
+      <c r="J36" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" s="29" t="s">
+      <c r="C37" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E37" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F37" s="31">
+      <c r="E37" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F37" s="17">
         <v>6</v>
       </c>
-      <c r="G37" s="31">
+      <c r="G37" s="17">
         <v>1</v>
       </c>
-      <c r="H37" s="31">
+      <c r="H37" s="17">
         <v>2</v>
       </c>
-      <c r="I37" s="31">
+      <c r="I37" s="17">
         <v>1</v>
       </c>
-      <c r="J37" s="31">
+      <c r="J37" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" s="29" t="s">
+      <c r="C38" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E38" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F38" s="31">
+      <c r="E38" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F38" s="17">
         <v>2</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="17">
         <v>9</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="17">
         <v>7</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="17">
         <v>1</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D39" s="29" t="s">
+      <c r="C39" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D39" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E39" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="31">
+      <c r="E39" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F39" s="17">
         <v>6</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="17">
         <v>8</v>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="17">
         <v>0</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="17">
         <v>10</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="17">
         <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D40" s="29" t="s">
+      <c r="D40" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E40" s="29" t="s">
+      <c r="E40" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F40" s="31">
+      <c r="F40" s="17">
         <v>5</v>
       </c>
-      <c r="G40" s="31">
+      <c r="G40" s="17">
         <v>6</v>
       </c>
-      <c r="H40" s="31">
+      <c r="H40" s="17">
         <v>4</v>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="17">
         <v>3</v>
       </c>
-      <c r="J40" s="31">
+      <c r="J40" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="B41" s="29" t="s">
+      <c r="B41" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C41" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41" s="29" t="s">
+      <c r="C41" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D41" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E41" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F41" s="31">
+      <c r="E41" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" s="17">
         <v>6</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="17">
         <v>1</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="17">
         <v>4</v>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="17">
         <v>1</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B42" s="29" t="s">
+      <c r="B42" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" s="29" t="s">
+      <c r="C42" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E42" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F42" s="31">
+      <c r="E42" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F42" s="17">
         <v>7</v>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="17">
         <v>1</v>
       </c>
-      <c r="H42" s="31">
+      <c r="H42" s="17">
         <v>10</v>
       </c>
-      <c r="I42" s="31">
+      <c r="I42" s="17">
         <v>2</v>
       </c>
-      <c r="J42" s="31">
+      <c r="J42" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D43" s="29" t="s">
+      <c r="D43" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E43" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F43" s="31">
+      <c r="E43" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F43" s="17">
         <v>9</v>
       </c>
-      <c r="G43" s="31">
+      <c r="G43" s="17">
         <v>3</v>
       </c>
-      <c r="H43" s="31">
+      <c r="H43" s="17">
         <v>8</v>
       </c>
-      <c r="I43" s="31">
+      <c r="I43" s="17">
         <v>2</v>
       </c>
-      <c r="J43" s="31">
+      <c r="J43" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="29" t="s">
+      <c r="A44" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44" s="29" t="s">
+      <c r="C44" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D44" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E44" s="29" t="s">
+      <c r="E44" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="17">
         <v>7</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="17">
         <v>8</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="17">
         <v>5</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="17">
         <v>5</v>
       </c>
-      <c r="J44" s="31">
+      <c r="J44" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="29" t="s">
+      <c r="A45" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D45" s="29" t="s">
+      <c r="D45" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E45" s="29" t="s">
+      <c r="E45" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="17">
         <v>9</v>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="17">
         <v>3</v>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="17">
         <v>9</v>
       </c>
-      <c r="I45" s="31">
+      <c r="I45" s="17">
         <v>2</v>
       </c>
-      <c r="J45" s="31">
+      <c r="J45" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="29" t="s">
+      <c r="B46" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C46" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D46" s="29" t="s">
+      <c r="C46" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E46" s="29" t="s">
+      <c r="E46" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F46" s="31">
+      <c r="F46" s="17">
         <v>10</v>
       </c>
-      <c r="G46" s="31">
+      <c r="G46" s="17">
         <v>2</v>
       </c>
-      <c r="H46" s="31">
+      <c r="H46" s="17">
         <v>9</v>
       </c>
-      <c r="I46" s="31">
+      <c r="I46" s="17">
         <v>2</v>
       </c>
-      <c r="J46" s="31">
+      <c r="J46" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C47" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D47" s="29" t="s">
+      <c r="C47" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E47" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F47" s="31">
+      <c r="E47" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F47" s="17">
         <v>2</v>
       </c>
-      <c r="G47" s="31">
+      <c r="G47" s="17">
         <v>7</v>
       </c>
-      <c r="H47" s="31">
+      <c r="H47" s="17">
         <v>5</v>
       </c>
-      <c r="I47" s="31">
+      <c r="I47" s="17">
         <v>1</v>
       </c>
-      <c r="J47" s="31">
+      <c r="J47" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="29" t="s">
+      <c r="A48" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B48" s="29" t="s">
+      <c r="B48" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C48" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D48" s="29" t="s">
+      <c r="C48" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E48" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F48" s="31">
+      <c r="E48" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F48" s="17">
         <v>3</v>
       </c>
-      <c r="G48" s="31">
+      <c r="G48" s="17">
         <v>8</v>
       </c>
-      <c r="H48" s="31">
+      <c r="H48" s="17">
         <v>1</v>
       </c>
-      <c r="I48" s="31">
+      <c r="I48" s="17">
         <v>5</v>
       </c>
-      <c r="J48" s="31">
+      <c r="J48" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="29" t="s">
+      <c r="B49" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D49" s="29" t="s">
+      <c r="D49" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E49" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F49" s="31">
+      <c r="E49" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F49" s="17">
         <v>9</v>
       </c>
-      <c r="G49" s="31">
+      <c r="G49" s="17">
         <v>3</v>
       </c>
-      <c r="H49" s="31">
+      <c r="H49" s="17">
         <v>9</v>
       </c>
-      <c r="I49" s="31">
+      <c r="I49" s="17">
         <v>2</v>
       </c>
-      <c r="J49" s="31">
+      <c r="J49" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="29" t="s">
+      <c r="A50" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="29" t="s">
+      <c r="B50" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C50" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D50" s="29" t="s">
+      <c r="C50" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E50" s="29" t="s">
+      <c r="E50" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="17">
         <v>7</v>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="17">
         <v>6</v>
       </c>
-      <c r="H50" s="31">
+      <c r="H50" s="17">
         <v>8</v>
       </c>
-      <c r="I50" s="31">
+      <c r="I50" s="17">
         <v>7</v>
       </c>
-      <c r="J50" s="31">
+      <c r="J50" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="29" t="s">
+      <c r="A51" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B51" s="29" t="s">
+      <c r="B51" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D51" s="29" t="s">
+      <c r="C51" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D51" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="29" t="s">
+      <c r="E51" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="17">
         <v>3</v>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="17">
         <v>8</v>
       </c>
-      <c r="H51" s="31">
+      <c r="H51" s="17">
         <v>1</v>
       </c>
-      <c r="I51" s="31">
+      <c r="I51" s="17">
         <v>4</v>
       </c>
-      <c r="J51" s="31">
+      <c r="J51" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="29" t="s">
+      <c r="B52" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C52" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D52" s="29" t="s">
+      <c r="C52" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D52" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E52" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F52" s="31">
+      <c r="E52" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F52" s="17">
         <v>2</v>
       </c>
-      <c r="G52" s="31">
+      <c r="G52" s="17">
         <v>8</v>
       </c>
-      <c r="H52" s="31">
+      <c r="H52" s="17">
         <v>3</v>
       </c>
-      <c r="I52" s="31">
+      <c r="I52" s="17">
         <v>1</v>
       </c>
-      <c r="J52" s="31">
+      <c r="J52" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="29" t="s">
+      <c r="A53" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C53" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D53" s="29" t="s">
+      <c r="C53" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D53" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E53" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F53" s="31">
+      <c r="E53" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F53" s="17">
         <v>4</v>
       </c>
-      <c r="G53" s="31">
+      <c r="G53" s="17">
         <v>8</v>
       </c>
-      <c r="H53" s="31">
+      <c r="H53" s="17">
         <v>2</v>
       </c>
-      <c r="I53" s="31">
+      <c r="I53" s="17">
         <v>5</v>
       </c>
-      <c r="J53" s="31">
+      <c r="J53" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="29" t="s">
+      <c r="A54" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B54" s="29" t="s">
+      <c r="B54" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C54" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D54" s="29" t="s">
+      <c r="C54" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D54" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E54" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F54" s="31">
+      <c r="E54" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F54" s="17">
         <v>4</v>
       </c>
-      <c r="G54" s="31">
+      <c r="G54" s="17">
         <v>8</v>
       </c>
-      <c r="H54" s="31">
+      <c r="H54" s="17">
         <v>2</v>
       </c>
-      <c r="I54" s="31">
+      <c r="I54" s="17">
         <v>5</v>
       </c>
-      <c r="J54" s="31">
+      <c r="J54" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B55" s="29" t="s">
+      <c r="B55" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D55" s="29" t="s">
+      <c r="D55" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E55" s="29" t="s">
+      <c r="E55" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="F55" s="31">
+      <c r="F55" s="17">
         <v>3</v>
       </c>
-      <c r="G55" s="31">
+      <c r="G55" s="17">
         <v>8</v>
       </c>
-      <c r="H55" s="31">
+      <c r="H55" s="17">
         <v>1</v>
       </c>
-      <c r="I55" s="31">
+      <c r="I55" s="17">
         <v>5</v>
       </c>
-      <c r="J55" s="31">
+      <c r="J55" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="29" t="s">
+      <c r="B56" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C56" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D56" s="29" t="s">
+      <c r="C56" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E56" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F56" s="31">
+      <c r="E56" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F56" s="17">
         <v>5</v>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="17">
         <v>8</v>
       </c>
-      <c r="H56" s="31">
+      <c r="H56" s="17">
         <v>1</v>
       </c>
-      <c r="I56" s="31">
+      <c r="I56" s="17">
         <v>6</v>
       </c>
-      <c r="J56" s="31">
+      <c r="J56" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="29" t="s">
+      <c r="A57" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B57" s="29" t="s">
+      <c r="B57" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D57" s="29" t="s">
+      <c r="C57" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E57" s="29" t="s">
+      <c r="E57" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="17">
         <v>4</v>
       </c>
-      <c r="G57" s="31">
+      <c r="G57" s="17">
         <v>7</v>
       </c>
-      <c r="H57" s="31">
+      <c r="H57" s="17">
         <v>3</v>
       </c>
-      <c r="I57" s="31">
+      <c r="I57" s="17">
         <v>4</v>
       </c>
-      <c r="J57" s="31">
+      <c r="J57" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B58" s="29" t="s">
+      <c r="B58" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="29" t="s">
+      <c r="D58" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E58" s="29" t="s">
+      <c r="E58" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F58" s="31">
+      <c r="F58" s="17">
         <v>9</v>
       </c>
-      <c r="G58" s="31">
+      <c r="G58" s="17">
         <v>5</v>
       </c>
-      <c r="H58" s="31">
+      <c r="H58" s="17">
         <v>5</v>
       </c>
-      <c r="I58" s="31">
+      <c r="I58" s="17">
         <v>5</v>
       </c>
-      <c r="J58" s="31">
+      <c r="J58" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="29" t="s">
+      <c r="A59" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B59" s="29" t="s">
+      <c r="B59" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C59" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D59" s="29" t="s">
+      <c r="C59" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E59" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F59" s="31">
+      <c r="E59" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F59" s="17">
         <v>10</v>
       </c>
-      <c r="G59" s="31">
+      <c r="G59" s="17">
         <v>2</v>
       </c>
-      <c r="H59" s="31">
+      <c r="H59" s="17">
         <v>9</v>
       </c>
-      <c r="I59" s="31">
+      <c r="I59" s="17">
         <v>2</v>
       </c>
-      <c r="J59" s="31">
+      <c r="J59" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="29" t="s">
+      <c r="A60" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B60" s="29" t="s">
+      <c r="B60" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C60" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D60" s="29" t="s">
+      <c r="C60" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E60" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F60" s="31">
+      <c r="E60" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F60" s="17">
         <v>2</v>
       </c>
-      <c r="G60" s="31">
+      <c r="G60" s="17">
         <v>8</v>
       </c>
-      <c r="H60" s="31">
+      <c r="H60" s="17">
         <v>1</v>
       </c>
-      <c r="I60" s="31">
+      <c r="I60" s="17">
         <v>4</v>
       </c>
-      <c r="J60" s="31">
+      <c r="J60" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="B61" s="29" t="s">
+      <c r="B61" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C61" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D61" s="29" t="s">
+      <c r="C61" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E61" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F61" s="31">
+      <c r="E61" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F61" s="17">
         <v>3</v>
       </c>
-      <c r="G61" s="31">
+      <c r="G61" s="17">
         <v>8</v>
       </c>
-      <c r="H61" s="31">
+      <c r="H61" s="17">
         <v>3</v>
       </c>
-      <c r="I61" s="31">
+      <c r="I61" s="17">
         <v>1</v>
       </c>
-      <c r="J61" s="31">
+      <c r="J61" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="29" t="s">
+      <c r="A62" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="B62" s="29" t="s">
+      <c r="B62" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C62" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D62" s="29" t="s">
+      <c r="C62" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D62" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E62" s="29" t="s">
+      <c r="E62" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="17">
         <v>7</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="17">
         <v>4</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="17">
         <v>6</v>
       </c>
-      <c r="I62" s="31">
+      <c r="I62" s="17">
         <v>3</v>
       </c>
-      <c r="J62" s="31">
+      <c r="J62" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="29" t="s">
+      <c r="A63" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B63" s="29" t="s">
+      <c r="B63" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="D63" s="29" t="s">
+      <c r="D63" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E63" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F63" s="31">
+      <c r="E63" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F63" s="17">
         <v>8</v>
       </c>
-      <c r="G63" s="31">
+      <c r="G63" s="17">
         <v>3</v>
       </c>
-      <c r="H63" s="31">
+      <c r="H63" s="17">
         <v>7</v>
       </c>
-      <c r="I63" s="31">
+      <c r="I63" s="17">
         <v>5</v>
       </c>
-      <c r="J63" s="31">
+      <c r="J63" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B64" s="29" t="s">
+      <c r="B64" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C64" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D64" s="29" t="s">
+      <c r="C64" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D64" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E64" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F64" s="31">
+      <c r="E64" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F64" s="17">
         <v>4</v>
       </c>
-      <c r="G64" s="31">
+      <c r="G64" s="17">
         <v>9</v>
       </c>
-      <c r="H64" s="31">
+      <c r="H64" s="17">
         <v>1</v>
       </c>
-      <c r="I64" s="31">
+      <c r="I64" s="17">
         <v>7</v>
       </c>
-      <c r="J64" s="31">
+      <c r="J64" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="29" t="s">
+      <c r="A65" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B65" s="29" t="s">
+      <c r="B65" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D65" s="29" t="s">
+      <c r="D65" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E65" s="29" t="s">
+      <c r="E65" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="17">
         <v>5</v>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="17">
         <v>8</v>
       </c>
-      <c r="H65" s="31">
+      <c r="H65" s="17">
         <v>5</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="17">
         <v>4</v>
       </c>
-      <c r="J65" s="31">
+      <c r="J65" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="B66" s="29" t="s">
+      <c r="B66" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E66" s="29" t="s">
+      <c r="E66" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F66" s="31">
+      <c r="F66" s="17">
         <v>3</v>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="17">
         <v>8</v>
       </c>
-      <c r="H66" s="31">
+      <c r="H66" s="17">
         <v>8</v>
       </c>
-      <c r="I66" s="31">
+      <c r="I66" s="17">
         <v>3</v>
       </c>
-      <c r="J66" s="31">
+      <c r="J66" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="29" t="s">
+      <c r="A67" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B67" s="29" t="s">
+      <c r="B67" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C67" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D67" s="29" t="s">
+      <c r="C67" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D67" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E67" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F67" s="31">
+      <c r="E67" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F67" s="17">
         <v>3</v>
       </c>
-      <c r="G67" s="31">
+      <c r="G67" s="17">
         <v>9</v>
       </c>
-      <c r="H67" s="31">
+      <c r="H67" s="17">
         <v>6</v>
       </c>
-      <c r="I67" s="31">
+      <c r="I67" s="17">
         <v>3</v>
       </c>
-      <c r="J67" s="31">
+      <c r="J67" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B68" s="29" t="s">
+      <c r="B68" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D68" s="29" t="s">
+      <c r="D68" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E68" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F68" s="31">
+      <c r="E68" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F68" s="17">
         <v>7</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="17">
         <v>3</v>
       </c>
-      <c r="H68" s="31">
+      <c r="H68" s="17">
         <v>8</v>
       </c>
-      <c r="I68" s="31">
+      <c r="I68" s="17">
         <v>3</v>
       </c>
-      <c r="J68" s="31">
+      <c r="J68" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B69" s="29" t="s">
+      <c r="B69" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D69" s="29" t="s">
+      <c r="D69" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E69" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F69" s="31">
+      <c r="E69" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F69" s="17">
         <v>6</v>
       </c>
-      <c r="G69" s="31">
+      <c r="G69" s="17">
         <v>2</v>
       </c>
-      <c r="H69" s="31">
+      <c r="H69" s="17">
         <v>8</v>
       </c>
-      <c r="I69" s="31">
+      <c r="I69" s="17">
         <v>4</v>
       </c>
-      <c r="J69" s="31">
+      <c r="J69" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="29" t="s">
+      <c r="A70" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="B70" s="29" t="s">
+      <c r="B70" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C70" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D70" s="29" t="s">
+      <c r="C70" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D70" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E70" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F70" s="31">
+      <c r="E70" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F70" s="17">
         <v>5</v>
       </c>
-      <c r="G70" s="31">
+      <c r="G70" s="17">
         <v>7</v>
       </c>
-      <c r="H70" s="31">
+      <c r="H70" s="17">
         <v>1</v>
       </c>
-      <c r="I70" s="31">
+      <c r="I70" s="17">
         <v>4</v>
       </c>
-      <c r="J70" s="31">
+      <c r="J70" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="29" t="s">
+      <c r="A71" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B71" s="29" t="s">
+      <c r="B71" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C71" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D71" s="29" t="s">
+      <c r="C71" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D71" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E71" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F71" s="31">
+      <c r="E71" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F71" s="17">
         <v>3</v>
       </c>
-      <c r="G71" s="31">
+      <c r="G71" s="17">
         <v>10</v>
       </c>
-      <c r="H71" s="31">
+      <c r="H71" s="17">
         <v>1</v>
       </c>
-      <c r="I71" s="31">
+      <c r="I71" s="17">
         <v>2</v>
       </c>
-      <c r="J71" s="31">
+      <c r="J71" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="29" t="s">
+      <c r="A72" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B72" s="29" t="s">
+      <c r="B72" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C72" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D72" s="29" t="s">
+      <c r="C72" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D72" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E72" s="29" t="s">
+      <c r="E72" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F72" s="31">
+      <c r="F72" s="17">
         <v>7</v>
       </c>
-      <c r="G72" s="31">
+      <c r="G72" s="17">
         <v>5</v>
       </c>
-      <c r="H72" s="31">
+      <c r="H72" s="17">
         <v>5</v>
       </c>
-      <c r="I72" s="31">
+      <c r="I72" s="17">
         <v>5</v>
       </c>
-      <c r="J72" s="31">
+      <c r="J72" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="29" t="s">
+      <c r="A73" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B73" s="29" t="s">
+      <c r="B73" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C73" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D73" s="29" t="s">
+      <c r="C73" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D73" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E73" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F73" s="31">
+      <c r="E73" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F73" s="17">
         <v>8</v>
       </c>
-      <c r="G73" s="31">
+      <c r="G73" s="17">
         <v>2</v>
       </c>
-      <c r="H73" s="31">
+      <c r="H73" s="17">
         <v>8</v>
       </c>
-      <c r="I73" s="31">
+      <c r="I73" s="17">
         <v>2</v>
       </c>
-      <c r="J73" s="31">
+      <c r="J73" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="29" t="s">
+      <c r="A74" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B74" s="29" t="s">
+      <c r="B74" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D74" s="29" t="s">
+      <c r="D74" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E74" s="29" t="s">
+      <c r="E74" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F74" s="31">
+      <c r="F74" s="17">
         <v>2</v>
       </c>
-      <c r="G74" s="31">
+      <c r="G74" s="17">
         <v>8</v>
       </c>
-      <c r="H74" s="31">
+      <c r="H74" s="17">
         <v>6</v>
       </c>
-      <c r="I74" s="31">
+      <c r="I74" s="17">
         <v>2</v>
       </c>
-      <c r="J74" s="31">
+      <c r="J74" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="29" t="s">
+      <c r="A75" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B75" s="29" t="s">
+      <c r="B75" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C75" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D75" s="29" t="s">
+      <c r="C75" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D75" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E75" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F75" s="31">
+      <c r="E75" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F75" s="17">
         <v>5</v>
       </c>
-      <c r="G75" s="31">
+      <c r="G75" s="17">
         <v>7</v>
       </c>
-      <c r="H75" s="31">
+      <c r="H75" s="17">
         <v>1</v>
       </c>
-      <c r="I75" s="31">
+      <c r="I75" s="17">
         <v>8</v>
       </c>
-      <c r="J75" s="31">
+      <c r="J75" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="29" t="s">
+      <c r="A76" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B76" s="29" t="s">
+      <c r="B76" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C76" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D76" s="29" t="s">
+      <c r="C76" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D76" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E76" s="29" t="s">
+      <c r="E76" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F76" s="31">
+      <c r="F76" s="17">
         <v>9</v>
       </c>
-      <c r="G76" s="31">
+      <c r="G76" s="17">
         <v>6</v>
       </c>
-      <c r="H76" s="31">
+      <c r="H76" s="17">
         <v>4</v>
       </c>
-      <c r="I76" s="31">
+      <c r="I76" s="17">
         <v>4</v>
       </c>
-      <c r="J76" s="31">
+      <c r="J76" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="29" t="s">
+      <c r="A77" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B77" s="29" t="s">
+      <c r="B77" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C77" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D77" s="29" t="s">
+      <c r="C77" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D77" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E77" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F77" s="31">
+      <c r="E77" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F77" s="17">
         <v>1</v>
       </c>
-      <c r="G77" s="31">
+      <c r="G77" s="17">
         <v>9</v>
       </c>
-      <c r="H77" s="31">
+      <c r="H77" s="17">
         <v>1</v>
       </c>
-      <c r="I77" s="31">
+      <c r="I77" s="17">
         <v>1</v>
       </c>
-      <c r="J77" s="31">
+      <c r="J77" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="29" t="s">
+      <c r="A78" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B78" s="29" t="s">
+      <c r="B78" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C78" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D78" s="29" t="s">
+      <c r="C78" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D78" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E78" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F78" s="31">
+      <c r="E78" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F78" s="17">
         <v>6</v>
       </c>
-      <c r="G78" s="31">
+      <c r="G78" s="17">
         <v>7</v>
       </c>
-      <c r="H78" s="31">
+      <c r="H78" s="17">
         <v>3</v>
       </c>
-      <c r="I78" s="31">
+      <c r="I78" s="17">
         <v>5</v>
       </c>
-      <c r="J78" s="31">
+      <c r="J78" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="29" t="s">
+      <c r="A79" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B79" s="29" t="s">
+      <c r="B79" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C79" s="29" t="s">
+      <c r="C79" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D79" s="29" t="s">
+      <c r="D79" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E79" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F79" s="31">
+      <c r="E79" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F79" s="17">
         <v>1</v>
       </c>
-      <c r="G79" s="31">
+      <c r="G79" s="17">
         <v>10</v>
       </c>
-      <c r="H79" s="31">
+      <c r="H79" s="17">
         <v>2</v>
       </c>
-      <c r="I79" s="31">
+      <c r="I79" s="17">
         <v>2</v>
       </c>
-      <c r="J79" s="31">
+      <c r="J79" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="29" t="s">
+      <c r="A80" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="B80" s="29" t="s">
+      <c r="B80" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C80" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D80" s="29" t="s">
+      <c r="C80" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D80" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E80" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F80" s="31">
+      <c r="E80" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F80" s="17">
         <v>4</v>
       </c>
-      <c r="G80" s="31">
+      <c r="G80" s="17">
         <v>8</v>
       </c>
-      <c r="H80" s="31">
+      <c r="H80" s="17">
         <v>2</v>
       </c>
-      <c r="I80" s="31">
+      <c r="I80" s="17">
         <v>9</v>
       </c>
-      <c r="J80" s="31">
+      <c r="J80" s="17">
         <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="29" t="s">
+      <c r="A81" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="B81" s="29" t="s">
+      <c r="B81" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C81" s="29" t="s">
+      <c r="C81" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D81" s="29" t="s">
+      <c r="D81" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E81" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F81" s="31">
+      <c r="E81" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F81" s="17">
         <v>8</v>
       </c>
-      <c r="G81" s="31">
+      <c r="G81" s="17">
         <v>1</v>
       </c>
-      <c r="H81" s="31">
+      <c r="H81" s="17">
         <v>8</v>
       </c>
-      <c r="I81" s="31">
+      <c r="I81" s="17">
         <v>2</v>
       </c>
-      <c r="J81" s="31">
+      <c r="J81" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="29" t="s">
+      <c r="A82" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B82" s="29" t="s">
+      <c r="B82" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C82" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D82" s="29" t="s">
+      <c r="C82" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D82" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E82" s="29" t="s">
+      <c r="E82" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F82" s="31">
+      <c r="F82" s="17">
         <v>8</v>
       </c>
-      <c r="G82" s="31">
+      <c r="G82" s="17">
         <v>7</v>
       </c>
-      <c r="H82" s="31">
+      <c r="H82" s="17">
         <v>3</v>
       </c>
-      <c r="I82" s="31">
+      <c r="I82" s="17">
         <v>3</v>
       </c>
-      <c r="J82" s="31">
+      <c r="J82" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="29" t="s">
+      <c r="A83" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B83" s="29" t="s">
+      <c r="B83" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C83" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D83" s="29" t="s">
+      <c r="C83" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D83" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E83" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F83" s="31">
+      <c r="E83" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F83" s="17">
         <v>5</v>
       </c>
-      <c r="G83" s="31">
+      <c r="G83" s="17">
         <v>10</v>
       </c>
-      <c r="H83" s="31">
+      <c r="H83" s="17">
         <v>2</v>
       </c>
-      <c r="I83" s="31">
+      <c r="I83" s="17">
         <v>3</v>
       </c>
-      <c r="J83" s="31">
+      <c r="J83" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="29" t="s">
+      <c r="A84" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B84" s="29" t="s">
+      <c r="B84" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C84" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D84" s="29" t="s">
+      <c r="C84" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D84" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E84" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F84" s="31">
+      <c r="E84" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F84" s="17">
         <v>3</v>
       </c>
-      <c r="G84" s="31">
+      <c r="G84" s="17">
         <v>8</v>
       </c>
-      <c r="H84" s="31">
+      <c r="H84" s="17">
         <v>6</v>
       </c>
-      <c r="I84" s="31">
+      <c r="I84" s="17">
         <v>1</v>
       </c>
-      <c r="J84" s="31">
+      <c r="J84" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="29" t="s">
+      <c r="A85" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B85" s="29" t="s">
+      <c r="B85" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C85" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D85" s="29" t="s">
+      <c r="C85" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D85" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E85" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F85" s="31">
+      <c r="E85" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F85" s="17">
         <v>4</v>
       </c>
-      <c r="G85" s="31">
+      <c r="G85" s="17">
         <v>8</v>
       </c>
-      <c r="H85" s="31">
+      <c r="H85" s="17">
         <v>2</v>
       </c>
-      <c r="I85" s="31">
+      <c r="I85" s="17">
         <v>2</v>
       </c>
-      <c r="J85" s="31">
+      <c r="J85" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="29" t="s">
+      <c r="A86" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B86" s="29" t="s">
+      <c r="B86" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C86" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D86" s="29" t="s">
+      <c r="C86" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D86" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="E86" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F86" s="31">
+      <c r="E86" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F86" s="17">
         <v>6</v>
       </c>
-      <c r="G86" s="31">
+      <c r="G86" s="17">
         <v>2</v>
       </c>
-      <c r="H86" s="31">
+      <c r="H86" s="17">
         <v>9</v>
       </c>
-      <c r="I86" s="31">
+      <c r="I86" s="17">
         <v>3</v>
       </c>
-      <c r="J86" s="31">
+      <c r="J86" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="29" t="s">
+      <c r="A87" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B87" s="29" t="s">
+      <c r="B87" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C87" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D87" s="29" t="s">
+      <c r="C87" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D87" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E87" s="29" t="s">
+      <c r="E87" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F87" s="31">
+      <c r="F87" s="17">
         <v>7</v>
       </c>
-      <c r="G87" s="31">
+      <c r="G87" s="17">
         <v>5</v>
       </c>
-      <c r="H87" s="31">
+      <c r="H87" s="17">
         <v>6</v>
       </c>
-      <c r="I87" s="31">
+      <c r="I87" s="17">
         <v>4</v>
       </c>
-      <c r="J87" s="31">
+      <c r="J87" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="29" t="s">
+      <c r="A88" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B88" s="29" t="s">
+      <c r="B88" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C88" s="29" t="s">
+      <c r="C88" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D88" s="29" t="s">
+      <c r="D88" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E88" s="29" t="s">
+      <c r="E88" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F88" s="31">
+      <c r="F88" s="17">
         <v>7</v>
       </c>
-      <c r="G88" s="31">
+      <c r="G88" s="17">
         <v>7</v>
       </c>
-      <c r="H88" s="31">
+      <c r="H88" s="17">
         <v>3</v>
       </c>
-      <c r="I88" s="31">
+      <c r="I88" s="17">
         <v>3</v>
       </c>
-      <c r="J88" s="31">
+      <c r="J88" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="29" t="s">
+      <c r="A89" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="B89" s="29" t="s">
+      <c r="B89" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C89" s="29" t="s">
+      <c r="C89" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D89" s="29" t="s">
+      <c r="D89" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E89" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F89" s="31">
+      <c r="E89" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F89" s="17">
         <v>5</v>
       </c>
-      <c r="G89" s="31">
+      <c r="G89" s="17">
         <v>2</v>
       </c>
-      <c r="H89" s="31">
+      <c r="H89" s="17">
         <v>4</v>
       </c>
-      <c r="I89" s="31">
+      <c r="I89" s="17">
         <v>4</v>
       </c>
-      <c r="J89" s="31">
+      <c r="J89" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="29" t="s">
+      <c r="A90" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="B90" s="29" t="s">
+      <c r="B90" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C90" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D90" s="29" t="s">
+      <c r="C90" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D90" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E90" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F90" s="31">
+      <c r="E90" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F90" s="17">
         <v>2</v>
       </c>
-      <c r="G90" s="31">
+      <c r="G90" s="17">
         <v>9</v>
       </c>
-      <c r="H90" s="31">
+      <c r="H90" s="17">
         <v>1</v>
       </c>
-      <c r="I90" s="31">
+      <c r="I90" s="17">
         <v>2</v>
       </c>
-      <c r="J90" s="31">
+      <c r="J90" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="29" t="s">
+      <c r="A91" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="B91" s="29" t="s">
+      <c r="B91" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C91" s="29" t="s">
+      <c r="C91" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="D91" s="29" t="s">
+      <c r="D91" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E91" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F91" s="31">
+      <c r="E91" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F91" s="17">
         <v>8</v>
       </c>
-      <c r="G91" s="31">
+      <c r="G91" s="17">
         <v>1</v>
       </c>
-      <c r="H91" s="31">
+      <c r="H91" s="17">
         <v>9</v>
       </c>
-      <c r="I91" s="31">
+      <c r="I91" s="17">
         <v>3</v>
       </c>
-      <c r="J91" s="31">
+      <c r="J91" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="29" t="s">
+      <c r="A92" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B92" s="29" t="s">
+      <c r="B92" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C92" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D92" s="29" t="s">
+      <c r="C92" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D92" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E92" s="29" t="s">
+      <c r="E92" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F92" s="31">
+      <c r="F92" s="17">
         <v>6</v>
       </c>
-      <c r="G92" s="31">
+      <c r="G92" s="17">
         <v>6</v>
       </c>
-      <c r="H92" s="31">
+      <c r="H92" s="17">
         <v>6</v>
       </c>
-      <c r="I92" s="31">
+      <c r="I92" s="17">
         <v>3</v>
       </c>
-      <c r="J92" s="31">
+      <c r="J92" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="29" t="s">
+      <c r="A93" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B93" s="29" t="s">
+      <c r="B93" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C93" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D93" s="29" t="s">
+      <c r="C93" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D93" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E93" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F93" s="31">
+      <c r="E93" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F93" s="17">
         <v>1</v>
       </c>
-      <c r="G93" s="31">
+      <c r="G93" s="17">
         <v>9</v>
       </c>
-      <c r="H93" s="31">
+      <c r="H93" s="17">
         <v>2</v>
       </c>
-      <c r="I93" s="31">
+      <c r="I93" s="17">
         <v>3</v>
       </c>
-      <c r="J93" s="31">
+      <c r="J93" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="29" t="s">
+      <c r="A94" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B94" s="29" t="s">
+      <c r="B94" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C94" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D94" s="29" t="s">
+      <c r="C94" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D94" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E94" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F94" s="31">
+      <c r="E94" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F94" s="17">
         <v>2</v>
       </c>
-      <c r="G94" s="31">
+      <c r="G94" s="17">
         <v>8</v>
       </c>
-      <c r="H94" s="31">
+      <c r="H94" s="17">
         <v>5</v>
       </c>
-      <c r="I94" s="31">
+      <c r="I94" s="17">
         <v>4</v>
       </c>
-      <c r="J94" s="31">
+      <c r="J94" s="17">
         <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="29" t="s">
+      <c r="A95" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="B95" s="29" t="s">
+      <c r="B95" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C95" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D95" s="29" t="s">
+      <c r="C95" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D95" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E95" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F95" s="31">
+      <c r="E95" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F95" s="17">
         <v>3</v>
       </c>
-      <c r="G95" s="31">
+      <c r="G95" s="17">
         <v>8</v>
       </c>
-      <c r="H95" s="31">
+      <c r="H95" s="17">
         <v>7</v>
       </c>
-      <c r="I95" s="31">
+      <c r="I95" s="17">
         <v>1</v>
       </c>
-      <c r="J95" s="31">
+      <c r="J95" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="29" t="s">
+      <c r="A96" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="B96" s="29" t="s">
+      <c r="B96" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C96" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D96" s="29" t="s">
+      <c r="C96" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D96" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E96" s="29" t="s">
+      <c r="E96" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F96" s="31">
+      <c r="F96" s="17">
         <v>3</v>
       </c>
-      <c r="G96" s="31">
+      <c r="G96" s="17">
         <v>7</v>
       </c>
-      <c r="H96" s="31">
+      <c r="H96" s="17">
         <v>3</v>
       </c>
-      <c r="I96" s="31">
+      <c r="I96" s="17">
         <v>4</v>
       </c>
-      <c r="J96" s="31">
+      <c r="J96" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="29" t="s">
+      <c r="A97" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B97" s="29" t="s">
+      <c r="B97" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C97" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D97" s="29" t="s">
+      <c r="C97" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D97" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E97" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F97" s="31">
+      <c r="E97" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F97" s="17">
         <v>2</v>
       </c>
-      <c r="G97" s="31">
+      <c r="G97" s="17">
         <v>9</v>
       </c>
-      <c r="H97" s="31">
+      <c r="H97" s="17">
         <v>3</v>
       </c>
-      <c r="I97" s="31">
+      <c r="I97" s="17">
         <v>3</v>
       </c>
-      <c r="J97" s="31">
+      <c r="J97" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="29" t="s">
+      <c r="A98" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B98" s="29" t="s">
+      <c r="B98" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C98" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D98" s="29" t="s">
+      <c r="C98" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D98" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E98" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F98" s="31">
+      <c r="E98" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F98" s="17">
         <v>4</v>
       </c>
-      <c r="G98" s="31">
+      <c r="G98" s="17">
         <v>8</v>
       </c>
-      <c r="H98" s="31">
+      <c r="H98" s="17">
         <v>2</v>
       </c>
-      <c r="I98" s="31">
+      <c r="I98" s="17">
         <v>8</v>
       </c>
-      <c r="J98" s="31">
+      <c r="J98" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="29" t="s">
+      <c r="A99" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B99" s="29" t="s">
+      <c r="B99" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C99" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D99" s="29" t="s">
+      <c r="C99" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D99" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E99" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F99" s="31">
+      <c r="E99" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F99" s="17">
         <v>2</v>
       </c>
-      <c r="G99" s="31">
+      <c r="G99" s="17">
         <v>9</v>
       </c>
-      <c r="H99" s="31">
+      <c r="H99" s="17">
         <v>2</v>
       </c>
-      <c r="I99" s="31">
+      <c r="I99" s="17">
         <v>5</v>
       </c>
-      <c r="J99" s="31">
+      <c r="J99" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="29" t="s">
+      <c r="A100" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B100" s="29" t="s">
+      <c r="B100" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C100" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D100" s="29" t="s">
+      <c r="C100" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D100" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E100" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F100" s="31">
+      <c r="E100" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F100" s="17">
         <v>2</v>
       </c>
-      <c r="G100" s="31">
+      <c r="G100" s="17">
         <v>8</v>
       </c>
-      <c r="H100" s="31">
+      <c r="H100" s="17">
         <v>4</v>
       </c>
-      <c r="I100" s="31">
+      <c r="I100" s="17">
         <v>5</v>
       </c>
-      <c r="J100" s="31">
+      <c r="J100" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="29" t="s">
+      <c r="A101" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="B101" s="29" t="s">
+      <c r="B101" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C101" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D101" s="29" t="s">
+      <c r="C101" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D101" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E101" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F101" s="31">
+      <c r="E101" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F101" s="17">
         <v>3</v>
       </c>
-      <c r="G101" s="31">
+      <c r="G101" s="17">
         <v>9</v>
       </c>
-      <c r="H101" s="31">
+      <c r="H101" s="17">
         <v>5</v>
       </c>
-      <c r="I101" s="31">
+      <c r="I101" s="17">
         <v>1</v>
       </c>
-      <c r="J101" s="31">
+      <c r="J101" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="29" t="s">
+      <c r="A102" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B102" s="29" t="s">
+      <c r="B102" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C102" s="29" t="s">
+      <c r="C102" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D102" s="29" t="s">
+      <c r="D102" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E102" s="29" t="s">
+      <c r="E102" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F102" s="31">
+      <c r="F102" s="17">
         <v>5</v>
       </c>
-      <c r="G102" s="31">
+      <c r="G102" s="17">
         <v>7</v>
       </c>
-      <c r="H102" s="31">
+      <c r="H102" s="17">
         <v>4</v>
       </c>
-      <c r="I102" s="31">
+      <c r="I102" s="17">
         <v>6</v>
       </c>
-      <c r="J102" s="31">
+      <c r="J102" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="29" t="s">
+      <c r="A103" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B103" s="29" t="s">
+      <c r="B103" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C103" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D103" s="29" t="s">
+      <c r="C103" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D103" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E103" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F103" s="31">
+      <c r="E103" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F103" s="17">
         <v>3</v>
       </c>
-      <c r="G103" s="31">
+      <c r="G103" s="17">
         <v>9</v>
       </c>
-      <c r="H103" s="31">
+      <c r="H103" s="17">
         <v>5</v>
       </c>
-      <c r="I103" s="31">
+      <c r="I103" s="17">
         <v>6</v>
       </c>
-      <c r="J103" s="31">
+      <c r="J103" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="29" t="s">
+      <c r="A104" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B104" s="29" t="s">
+      <c r="B104" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C104" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D104" s="29" t="s">
+      <c r="C104" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D104" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E104" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F104" s="31">
+      <c r="E104" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F104" s="17">
         <v>8</v>
       </c>
-      <c r="G104" s="31">
+      <c r="G104" s="17">
         <v>5</v>
       </c>
-      <c r="H104" s="31">
+      <c r="H104" s="17">
         <v>5</v>
       </c>
-      <c r="I104" s="31">
+      <c r="I104" s="17">
         <v>3</v>
       </c>
-      <c r="J104" s="31">
+      <c r="J104" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="29" t="s">
+      <c r="A105" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B105" s="29" t="s">
+      <c r="B105" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C105" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D105" s="29" t="s">
+      <c r="C105" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D105" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E105" s="29" t="s">
+      <c r="E105" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F105" s="31">
+      <c r="F105" s="17">
         <v>2</v>
       </c>
-      <c r="G105" s="31">
+      <c r="G105" s="17">
         <v>7</v>
       </c>
-      <c r="H105" s="31">
+      <c r="H105" s="17">
         <v>6</v>
       </c>
-      <c r="I105" s="31">
+      <c r="I105" s="17">
         <v>2</v>
       </c>
-      <c r="J105" s="31">
+      <c r="J105" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="29" t="s">
+      <c r="A106" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="B106" s="29" t="s">
+      <c r="B106" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C106" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D106" s="29" t="s">
+      <c r="C106" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D106" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E106" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F106" s="31">
+      <c r="E106" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F106" s="17">
         <v>6</v>
       </c>
-      <c r="G106" s="31">
+      <c r="G106" s="17">
         <v>1</v>
       </c>
-      <c r="H106" s="31">
+      <c r="H106" s="17">
         <v>6</v>
       </c>
-      <c r="I106" s="31">
+      <c r="I106" s="17">
         <v>2</v>
       </c>
-      <c r="J106" s="31">
+      <c r="J106" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="29" t="s">
+      <c r="A107" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B107" s="29" t="s">
+      <c r="B107" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C107" s="29" t="s">
+      <c r="C107" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="D107" s="29" t="s">
+      <c r="D107" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E107" s="29" t="s">
+      <c r="E107" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F107" s="31">
+      <c r="F107" s="17">
         <v>5</v>
       </c>
-      <c r="G107" s="31">
+      <c r="G107" s="17">
         <v>7</v>
       </c>
-      <c r="H107" s="31">
+      <c r="H107" s="17">
         <v>1</v>
       </c>
-      <c r="I107" s="31">
+      <c r="I107" s="17">
         <v>5</v>
       </c>
-      <c r="J107" s="31">
+      <c r="J107" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="29" t="s">
+      <c r="A108" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B108" s="29" t="s">
+      <c r="B108" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C108" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D108" s="29" t="s">
+      <c r="C108" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D108" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E108" s="29" t="s">
+      <c r="E108" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F108" s="31">
+      <c r="F108" s="17">
         <v>7</v>
       </c>
-      <c r="G108" s="31">
+      <c r="G108" s="17">
         <v>4</v>
       </c>
-      <c r="H108" s="31">
+      <c r="H108" s="17">
         <v>9</v>
       </c>
-      <c r="I108" s="31">
+      <c r="I108" s="17">
         <v>3</v>
       </c>
-      <c r="J108" s="31">
+      <c r="J108" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="29" t="s">
+      <c r="A109" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B109" s="29" t="s">
+      <c r="B109" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C109" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D109" s="29" t="s">
+      <c r="C109" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D109" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E109" s="29" t="s">
+      <c r="E109" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F109" s="31">
+      <c r="F109" s="17">
         <v>3</v>
       </c>
-      <c r="G109" s="31">
+      <c r="G109" s="17">
         <v>7</v>
       </c>
-      <c r="H109" s="31">
+      <c r="H109" s="17">
         <v>4</v>
       </c>
-      <c r="I109" s="31">
+      <c r="I109" s="17">
         <v>4</v>
       </c>
-      <c r="J109" s="31">
+      <c r="J109" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="29" t="s">
+      <c r="A110" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B110" s="29" t="s">
+      <c r="B110" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="29" t="s">
+      <c r="C110" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D110" s="29" t="s">
+      <c r="D110" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E110" s="29" t="s">
+      <c r="E110" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F110" s="31">
+      <c r="F110" s="17">
         <v>3</v>
       </c>
-      <c r="G110" s="31">
+      <c r="G110" s="17">
         <v>7</v>
       </c>
-      <c r="H110" s="31">
+      <c r="H110" s="17">
         <v>7</v>
       </c>
-      <c r="I110" s="31">
+      <c r="I110" s="17">
         <v>5</v>
       </c>
-      <c r="J110" s="31">
+      <c r="J110" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="29" t="s">
+      <c r="A111" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="B111" s="29" t="s">
+      <c r="B111" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C111" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D111" s="29" t="s">
+      <c r="C111" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D111" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E111" s="29" t="s">
+      <c r="E111" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F111" s="31">
+      <c r="F111" s="17">
         <v>6</v>
       </c>
-      <c r="G111" s="31">
+      <c r="G111" s="17">
         <v>6</v>
       </c>
-      <c r="H111" s="31">
+      <c r="H111" s="17">
         <v>5</v>
       </c>
-      <c r="I111" s="31">
+      <c r="I111" s="17">
         <v>3</v>
       </c>
-      <c r="J111" s="31">
+      <c r="J111" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="29" t="s">
+      <c r="A112" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="B112" s="29" t="s">
+      <c r="B112" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C112" s="29" t="s">
+      <c r="C112" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D112" s="29" t="s">
+      <c r="D112" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E112" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F112" s="31">
+      <c r="E112" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F112" s="17">
         <v>7</v>
       </c>
-      <c r="G112" s="31">
+      <c r="G112" s="17">
         <v>6</v>
       </c>
-      <c r="H112" s="31">
+      <c r="H112" s="17">
         <v>8</v>
       </c>
-      <c r="I112" s="31">
+      <c r="I112" s="17">
         <v>5</v>
       </c>
-      <c r="J112" s="31">
+      <c r="J112" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="29" t="s">
+      <c r="A113" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B113" s="29" t="s">
+      <c r="B113" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C113" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D113" s="29" t="s">
+      <c r="C113" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D113" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E113" s="29" t="s">
+      <c r="E113" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F113" s="31">
+      <c r="F113" s="17">
         <v>6</v>
       </c>
-      <c r="G113" s="31">
+      <c r="G113" s="17">
         <v>7</v>
       </c>
-      <c r="H113" s="31">
+      <c r="H113" s="17">
         <v>1</v>
       </c>
-      <c r="I113" s="31">
+      <c r="I113" s="17">
         <v>4</v>
       </c>
-      <c r="J113" s="31">
+      <c r="J113" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="29" t="s">
+      <c r="A114" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B114" s="29" t="s">
+      <c r="B114" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C114" s="29" t="s">
+      <c r="C114" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D114" s="29" t="s">
+      <c r="D114" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E114" s="29" t="s">
+      <c r="E114" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F114" s="31">
+      <c r="F114" s="17">
         <v>6</v>
       </c>
-      <c r="G114" s="31">
+      <c r="G114" s="17">
         <v>7</v>
       </c>
-      <c r="H114" s="31">
+      <c r="H114" s="17">
         <v>5</v>
       </c>
-      <c r="I114" s="31">
+      <c r="I114" s="17">
         <v>7</v>
       </c>
-      <c r="J114" s="31">
+      <c r="J114" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="29" t="s">
+      <c r="A115" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B115" s="29" t="s">
+      <c r="B115" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C115" s="29" t="s">
+      <c r="C115" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D115" s="29" t="s">
+      <c r="D115" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E115" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F115" s="31">
+      <c r="E115" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F115" s="17">
         <v>9</v>
       </c>
-      <c r="G115" s="31">
+      <c r="G115" s="17">
         <v>3</v>
       </c>
-      <c r="H115" s="31">
+      <c r="H115" s="17">
         <v>6</v>
       </c>
-      <c r="I115" s="31">
+      <c r="I115" s="17">
         <v>1</v>
       </c>
-      <c r="J115" s="31">
+      <c r="J115" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="29" t="s">
+      <c r="A116" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B116" s="29" t="s">
+      <c r="B116" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C116" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D116" s="29" t="s">
+      <c r="C116" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D116" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E116" s="29" t="s">
+      <c r="E116" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F116" s="31">
+      <c r="F116" s="17">
         <v>8</v>
       </c>
-      <c r="G116" s="31">
+      <c r="G116" s="17">
         <v>7</v>
       </c>
-      <c r="H116" s="31">
+      <c r="H116" s="17">
         <v>2</v>
       </c>
-      <c r="I116" s="31">
+      <c r="I116" s="17">
         <v>4</v>
       </c>
-      <c r="J116" s="31">
+      <c r="J116" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="29" t="s">
+      <c r="A117" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B117" s="29" t="s">
+      <c r="B117" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C117" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D117" s="29" t="s">
+      <c r="C117" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D117" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E117" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F117" s="31">
+      <c r="E117" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F117" s="17">
         <v>8</v>
       </c>
-      <c r="G117" s="31">
+      <c r="G117" s="17">
         <v>1</v>
       </c>
-      <c r="H117" s="31">
+      <c r="H117" s="17">
         <v>9</v>
       </c>
-      <c r="I117" s="31">
+      <c r="I117" s="17">
         <v>2</v>
       </c>
-      <c r="J117" s="31">
+      <c r="J117" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="29" t="s">
+      <c r="A118" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B118" s="29" t="s">
+      <c r="B118" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C118" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D118" s="29" t="s">
+      <c r="C118" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D118" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E118" s="29" t="s">
+      <c r="E118" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F118" s="31">
+      <c r="F118" s="17">
         <v>10</v>
       </c>
-      <c r="G118" s="31">
+      <c r="G118" s="17">
         <v>3</v>
       </c>
-      <c r="H118" s="31">
+      <c r="H118" s="17">
         <v>1</v>
       </c>
-      <c r="I118" s="31">
+      <c r="I118" s="17">
         <v>5</v>
       </c>
-      <c r="J118" s="31">
+      <c r="J118" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="29" t="s">
+      <c r="A119" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="B119" s="29" t="s">
+      <c r="B119" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C119" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D119" s="29" t="s">
+      <c r="C119" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D119" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E119" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F119" s="31">
+      <c r="E119" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F119" s="17">
         <v>2</v>
       </c>
-      <c r="G119" s="31">
+      <c r="G119" s="17">
         <v>8</v>
       </c>
-      <c r="H119" s="31">
+      <c r="H119" s="17">
         <v>7</v>
       </c>
-      <c r="I119" s="31">
+      <c r="I119" s="17">
         <v>3</v>
       </c>
-      <c r="J119" s="31">
+      <c r="J119" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="29" t="s">
+      <c r="A120" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B120" s="29" t="s">
+      <c r="B120" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C120" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D120" s="29" t="s">
+      <c r="C120" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D120" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E120" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F120" s="31">
+      <c r="E120" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F120" s="17">
         <v>5</v>
       </c>
-      <c r="G120" s="31">
+      <c r="G120" s="17">
         <v>8</v>
       </c>
-      <c r="H120" s="31">
+      <c r="H120" s="17">
         <v>6</v>
       </c>
-      <c r="I120" s="31">
+      <c r="I120" s="17">
         <v>6</v>
       </c>
-      <c r="J120" s="31">
+      <c r="J120" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="29" t="s">
+      <c r="A121" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B121" s="29" t="s">
+      <c r="B121" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C121" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D121" s="29" t="s">
+      <c r="C121" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D121" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E121" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F121" s="31">
+      <c r="E121" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F121" s="17">
         <v>3</v>
       </c>
-      <c r="G121" s="31">
+      <c r="G121" s="17">
         <v>6</v>
       </c>
-      <c r="H121" s="31">
+      <c r="H121" s="17">
         <v>6</v>
       </c>
-      <c r="I121" s="31">
+      <c r="I121" s="17">
         <v>1</v>
       </c>
-      <c r="J121" s="31">
+      <c r="J121" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="29" t="s">
+      <c r="A122" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B122" s="29" t="s">
+      <c r="B122" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C122" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D122" s="29" t="s">
+      <c r="C122" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D122" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E122" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F122" s="31">
+      <c r="E122" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F122" s="17">
         <v>2</v>
       </c>
-      <c r="G122" s="31">
+      <c r="G122" s="17">
         <v>8</v>
       </c>
-      <c r="H122" s="31">
+      <c r="H122" s="17">
         <v>7</v>
       </c>
-      <c r="I122" s="31">
+      <c r="I122" s="17">
         <v>1</v>
       </c>
-      <c r="J122" s="31">
+      <c r="J122" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="29" t="s">
+      <c r="A123" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="B123" s="29" t="s">
+      <c r="B123" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C123" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D123" s="29" t="s">
+      <c r="C123" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D123" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E123" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F123" s="31">
+      <c r="E123" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F123" s="17">
         <v>2</v>
       </c>
-      <c r="G123" s="31">
+      <c r="G123" s="17">
         <v>7</v>
       </c>
-      <c r="H123" s="31">
+      <c r="H123" s="17">
         <v>2</v>
       </c>
-      <c r="I123" s="31">
+      <c r="I123" s="17">
         <v>7</v>
       </c>
-      <c r="J123" s="31">
+      <c r="J123" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="29" t="s">
+      <c r="A124" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B124" s="29" t="s">
+      <c r="B124" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C124" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D124" s="29" t="s">
+      <c r="C124" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D124" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E124" s="29" t="s">
+      <c r="E124" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F124" s="31">
+      <c r="F124" s="17">
         <v>6</v>
       </c>
-      <c r="G124" s="31">
+      <c r="G124" s="17">
         <v>7</v>
       </c>
-      <c r="H124" s="31">
+      <c r="H124" s="17">
         <v>3</v>
       </c>
-      <c r="I124" s="31">
+      <c r="I124" s="17">
         <v>3</v>
       </c>
-      <c r="J124" s="31">
+      <c r="J124" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="29" t="s">
+      <c r="A125" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="B125" s="29" t="s">
+      <c r="B125" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C125" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D125" s="29" t="s">
+      <c r="C125" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D125" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E125" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F125" s="31">
+      <c r="E125" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F125" s="17">
         <v>2</v>
       </c>
-      <c r="G125" s="31">
+      <c r="G125" s="17">
         <v>9</v>
       </c>
-      <c r="H125" s="31">
+      <c r="H125" s="17">
         <v>6</v>
       </c>
-      <c r="I125" s="31">
+      <c r="I125" s="17">
         <v>1</v>
       </c>
-      <c r="J125" s="31">
+      <c r="J125" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="29" t="s">
+      <c r="A126" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B126" s="29" t="s">
+      <c r="B126" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C126" s="29" t="s">
+      <c r="C126" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="D126" s="29" t="s">
+      <c r="D126" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E126" s="29" t="s">
+      <c r="E126" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F126" s="31">
+      <c r="F126" s="17">
         <v>4</v>
       </c>
-      <c r="G126" s="31">
+      <c r="G126" s="17">
         <v>9</v>
       </c>
-      <c r="H126" s="31">
+      <c r="H126" s="17">
         <v>3</v>
       </c>
-      <c r="I126" s="31">
+      <c r="I126" s="17">
         <v>6</v>
       </c>
-      <c r="J126" s="31">
+      <c r="J126" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="29" t="s">
+      <c r="A127" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="B127" s="29" t="s">
+      <c r="B127" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C127" s="29" t="s">
+      <c r="C127" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D127" s="29" t="s">
+      <c r="D127" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E127" s="29" t="s">
+      <c r="E127" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F127" s="31">
+      <c r="F127" s="17">
         <v>4</v>
       </c>
-      <c r="G127" s="31">
+      <c r="G127" s="17">
         <v>7</v>
       </c>
-      <c r="H127" s="31">
+      <c r="H127" s="17">
         <v>4</v>
       </c>
-      <c r="I127" s="31">
+      <c r="I127" s="17">
         <v>4</v>
       </c>
-      <c r="J127" s="31">
+      <c r="J127" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="29" t="s">
+      <c r="A128" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B128" s="29" t="s">
+      <c r="B128" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C128" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D128" s="29" t="s">
+      <c r="C128" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D128" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E128" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F128" s="31">
+      <c r="E128" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F128" s="17">
         <v>7</v>
       </c>
-      <c r="G128" s="31">
+      <c r="G128" s="17">
         <v>7</v>
       </c>
-      <c r="H128" s="31">
+      <c r="H128" s="17">
         <v>5</v>
       </c>
-      <c r="I128" s="31">
+      <c r="I128" s="17">
         <v>3</v>
       </c>
-      <c r="J128" s="31">
+      <c r="J128" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="29" t="s">
+      <c r="A129" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B129" s="29" t="s">
+      <c r="B129" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C129" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D129" s="29" t="s">
+      <c r="C129" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D129" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E129" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F129" s="31">
+      <c r="E129" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F129" s="17">
         <v>4</v>
       </c>
-      <c r="G129" s="31">
+      <c r="G129" s="17">
         <v>8</v>
       </c>
-      <c r="H129" s="31">
+      <c r="H129" s="17">
         <v>7</v>
       </c>
-      <c r="I129" s="31">
+      <c r="I129" s="17">
         <v>1</v>
       </c>
-      <c r="J129" s="31">
+      <c r="J129" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="29" t="s">
+      <c r="A130" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B130" s="29" t="s">
+      <c r="B130" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C130" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D130" s="29" t="s">
+      <c r="C130" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D130" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E130" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F130" s="31">
+      <c r="E130" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F130" s="17">
         <v>3</v>
       </c>
-      <c r="G130" s="31">
+      <c r="G130" s="17">
         <v>8</v>
       </c>
-      <c r="H130" s="31">
+      <c r="H130" s="17">
         <v>5</v>
       </c>
-      <c r="I130" s="31">
+      <c r="I130" s="17">
         <v>1</v>
       </c>
-      <c r="J130" s="31">
+      <c r="J130" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="29" t="s">
+      <c r="A131" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B131" s="29" t="s">
+      <c r="B131" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C131" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D131" s="29" t="s">
+      <c r="C131" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D131" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E131" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F131" s="31">
+      <c r="E131" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F131" s="17">
         <v>3</v>
       </c>
-      <c r="G131" s="31">
+      <c r="G131" s="17">
         <v>9</v>
       </c>
-      <c r="H131" s="31">
+      <c r="H131" s="17">
         <v>4</v>
       </c>
-      <c r="I131" s="31">
+      <c r="I131" s="17">
         <v>2</v>
       </c>
-      <c r="J131" s="31">
+      <c r="J131" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="29" t="s">
+      <c r="A132" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B132" s="29" t="s">
+      <c r="B132" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C132" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D132" s="29" t="s">
+      <c r="C132" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D132" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E132" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F132" s="31">
+      <c r="E132" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F132" s="17">
         <v>6</v>
       </c>
-      <c r="G132" s="31">
+      <c r="G132" s="17">
         <v>7</v>
       </c>
-      <c r="H132" s="31">
+      <c r="H132" s="17">
         <v>8</v>
       </c>
-      <c r="I132" s="31">
+      <c r="I132" s="17">
         <v>3</v>
       </c>
-      <c r="J132" s="31">
+      <c r="J132" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="29" t="s">
+      <c r="A133" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="B133" s="29" t="s">
+      <c r="B133" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C133" s="29" t="s">
+      <c r="C133" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D133" s="29" t="s">
+      <c r="D133" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E133" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F133" s="31">
+      <c r="E133" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F133" s="17">
         <v>4</v>
       </c>
-      <c r="G133" s="31">
+      <c r="G133" s="17">
         <v>8</v>
       </c>
-      <c r="H133" s="31">
+      <c r="H133" s="17">
         <v>4</v>
       </c>
-      <c r="I133" s="31">
+      <c r="I133" s="17">
         <v>4</v>
       </c>
-      <c r="J133" s="31">
+      <c r="J133" s="17">
         <v>6</v>
       </c>
     </row>
@@ -15932,23 +16018,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="76f936ad-b0cb-40da-b269-8ff7e25c05c5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC378B3CF6D2434DBA1499C7B7782C8C" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7e7ad43e2ed59e8044b967b3e683b952">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="76f936ad-b0cb-40da-b269-8ff7e25c05c5" xmlns:ns4="75603a06-7a7d-4920-88f8-892590697369" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8c6cb50e0e475b53c2b2d6f1d322fab9" ns3:_="" ns4:_="">
     <xsd:import namespace="76f936ad-b0cb-40da-b269-8ff7e25c05c5"/>
@@ -16169,25 +16238,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE7C2246-CC0F-45BD-B1C0-7B559C74A41F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="76f936ad-b0cb-40da-b269-8ff7e25c05c5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CF10F82-32B0-4E4D-83AD-C460D61FEB2B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="76f936ad-b0cb-40da-b269-8ff7e25c05c5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{586026F6-AE76-4A49-800C-213D6511A347}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16204,4 +16272,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CF10F82-32B0-4E4D-83AD-C460D61FEB2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE7C2246-CC0F-45BD-B1C0-7B559C74A41F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="76f936ad-b0cb-40da-b269-8ff7e25c05c5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Analyst.xlsx
+++ b/Analyst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\MLBB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17490CAC-6E1D-44C3-9D0D-5721024461DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9797E5-B3B5-460E-9CE3-E5A1A732FB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{BF18B510-6A1A-4009-95A3-8CBEC6D17C32}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="195">
   <si>
     <t>Team</t>
   </si>
@@ -614,9 +614,6 @@
   </si>
   <si>
     <t>Rafaela</t>
-  </si>
-  <si>
-    <t>Yi Sun-Shin</t>
   </si>
   <si>
     <t>MPL ID S17</t>
@@ -922,47 +919,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1000,86 +957,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1649,7 +1526,7 @@
         <v>52</v>
       </c>
       <c r="Z4" s="4" t="str">
-        <f t="shared" ref="Z4:Z65" si="0">IF(N4="WIN","LOSE","WIN")</f>
+        <f t="shared" ref="Z4:Z32" si="0">IF(N4="WIN","LOSE","WIN")</f>
         <v>LOSE</v>
       </c>
     </row>
@@ -3473,7 +3350,7 @@
         <v>31</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>41</v>
@@ -3533,13 +3410,13 @@
     </row>
     <row r="28" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>40</v>
@@ -3614,13 +3491,13 @@
     </row>
     <row r="29" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>40</v>
@@ -3695,7 +3572,7 @@
     </row>
     <row r="30" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>90</v>
@@ -3737,7 +3614,7 @@
         <v>92</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>78</v>
@@ -3776,13 +3653,13 @@
     </row>
     <row r="31" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>50</v>
@@ -3818,7 +3695,7 @@
         <v>82</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>25</v>
@@ -3857,13 +3734,13 @@
     </row>
     <row r="32" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>56</v>
@@ -3899,7 +3776,7 @@
         <v>92</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>19</v>
@@ -3957,18 +3834,18 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="N1:N3">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
       <formula>"LOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
       <formula>"WIN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N1048576 Z1:Z1048576">
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="11" operator="equal">
       <formula>"win"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
       <formula>"lose"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8255,23 +8132,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="76f936ad-b0cb-40da-b269-8ff7e25c05c5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC378B3CF6D2434DBA1499C7B7782C8C" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7e7ad43e2ed59e8044b967b3e683b952">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="76f936ad-b0cb-40da-b269-8ff7e25c05c5" xmlns:ns4="75603a06-7a7d-4920-88f8-892590697369" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8c6cb50e0e475b53c2b2d6f1d322fab9" ns3:_="" ns4:_="">
     <xsd:import namespace="76f936ad-b0cb-40da-b269-8ff7e25c05c5"/>
@@ -8492,25 +8352,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE7C2246-CC0F-45BD-B1C0-7B559C74A41F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="76f936ad-b0cb-40da-b269-8ff7e25c05c5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CF10F82-32B0-4E4D-83AD-C460D61FEB2B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="76f936ad-b0cb-40da-b269-8ff7e25c05c5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{586026F6-AE76-4A49-800C-213D6511A347}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8527,4 +8386,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CF10F82-32B0-4E4D-83AD-C460D61FEB2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE7C2246-CC0F-45BD-B1C0-7B559C74A41F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="76f936ad-b0cb-40da-b269-8ff7e25c05c5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Analyst.xlsx
+++ b/Analyst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\MLBB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9797E5-B3B5-460E-9CE3-E5A1A732FB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F7F348-07C6-4F6F-B31A-52F0F0481AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{BF18B510-6A1A-4009-95A3-8CBEC6D17C32}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="199">
   <si>
     <t>Team</t>
   </si>
@@ -626,6 +626,18 @@
   </si>
   <si>
     <t>RRQ</t>
+  </si>
+  <si>
+    <t>EVOS</t>
+  </si>
+  <si>
+    <t>GEEK</t>
+  </si>
+  <si>
+    <t>X Borg</t>
+  </si>
+  <si>
+    <t>ONIC</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1290,7 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:AO32"/>
+  <dimension ref="A1:AO40"/>
   <sheetFormatPr defaultColWidth="12.69921875" defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.69921875" style="10"/>
@@ -1526,7 +1538,7 @@
         <v>52</v>
       </c>
       <c r="Z4" s="4" t="str">
-        <f t="shared" ref="Z4:Z32" si="0">IF(N4="WIN","LOSE","WIN")</f>
+        <f t="shared" ref="Z4:Z40" si="0">IF(N4="WIN","LOSE","WIN")</f>
         <v>LOSE</v>
       </c>
     </row>
@@ -3811,6 +3823,654 @@
       <c r="Z32" s="4" t="str">
         <f t="shared" si="0"/>
         <v>WIN</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>LOSE</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z34" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>LOSE</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z35" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>WIN</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z36" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>LOSE</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z37" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>WIN</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z38" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>LOSE</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z39" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>LOSE</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y40" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z40" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>LOSE</v>
       </c>
     </row>
   </sheetData>
@@ -8132,6 +8792,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="76f936ad-b0cb-40da-b269-8ff7e25c05c5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC378B3CF6D2434DBA1499C7B7782C8C" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7e7ad43e2ed59e8044b967b3e683b952">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="76f936ad-b0cb-40da-b269-8ff7e25c05c5" xmlns:ns4="75603a06-7a7d-4920-88f8-892590697369" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8c6cb50e0e475b53c2b2d6f1d322fab9" ns3:_="" ns4:_="">
     <xsd:import namespace="76f936ad-b0cb-40da-b269-8ff7e25c05c5"/>
@@ -8352,24 +9029,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE7C2246-CC0F-45BD-B1C0-7B559C74A41F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="76f936ad-b0cb-40da-b269-8ff7e25c05c5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="76f936ad-b0cb-40da-b269-8ff7e25c05c5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CF10F82-32B0-4E4D-83AD-C460D61FEB2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{586026F6-AE76-4A49-800C-213D6511A347}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8386,22 +9064,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CF10F82-32B0-4E4D-83AD-C460D61FEB2B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE7C2246-CC0F-45BD-B1C0-7B559C74A41F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="76f936ad-b0cb-40da-b269-8ff7e25c05c5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>